--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -5946,7 +5946,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -5946,7 +5946,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>puppy</t>
+          <t>filhote</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -5888,7 +5888,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>filhote</t>
+          <t>puppy</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petlove_20260407_203651.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
